--- a/data/raw/emission_factors.xlsx
+++ b/data/raw/emission_factors.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11012"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haukeschlesier/FFEI_copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haukeschlesier/FFEI/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6272EBAA-64A6-B14F-A170-BCA5FA9FEBDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB909595-DC45-C543-8FA8-F6C4E2AAFA39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="39">
   <si>
     <t>CO2</t>
   </si>
@@ -183,6 +183,9 @@
   </si>
   <si>
     <t>https://ghgprotocol.org/sites/default/files/ghgp/Emission_Factors_from_Cross_Sector_Tools_March_2017.xlsx</t>
+  </si>
+  <si>
+    <t>water pump operation, diesel</t>
   </si>
 </sst>
 </file>
@@ -270,8 +273,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -597,7 +602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="42.5" style="2" bestFit="1" customWidth="1"/>
@@ -1036,7 +1041,7 @@
       <c r="D22" s="7">
         <v>1.8588960223067522E-4</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="9" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="6" t="s">
@@ -1047,13 +1052,13 @@
       <c r="A23" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="6">
         <v>0</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="6">
         <v>0</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="6">
         <v>0</v>
       </c>
       <c r="E23" s="6" t="s">
@@ -1127,6 +1132,26 @@
       </c>
       <c r="F26" s="6" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="8">
+        <v>0</v>
+      </c>
+      <c r="C27" s="7">
+        <v>0</v>
+      </c>
+      <c r="D27" s="7">
+        <v>0</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
